--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487802_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487802_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2005</v>
+        <v>5.6659</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0725</v>
+        <v>7.1251</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.872</v>
+        <v>-1.4592</v>
       </c>
       <c r="G2" t="n">
         <v>3.2393</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>5.212</v>
+        <v>2.6775</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6587</v>
+        <v>2.7113</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5533</v>
+        <v>-0.0339</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2914</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9888</v>
+        <v>1.7952</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1822</v>
+        <v>3.8125</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1934</v>
+        <v>-2.0173</v>
       </c>
       <c r="G3" t="n">
         <v>1.8614</v>
@@ -688,13 +688,13 @@
         <v>1.0406</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5182</v>
+        <v>1.3247</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0218</v>
+        <v>1.6521</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5036</v>
+        <v>-0.3275</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3503</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1852</v>
+        <v>0.4675</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3176</v>
+        <v>4.2244</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.1325</v>
+        <v>-3.7569</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1749</v>
+        <v>-2.8921</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6967</v>
+        <v>-1.7033</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5218</v>
+        <v>-1.1887</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2002</v>
+        <v>1.2435</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3381</v>
+        <v>-0.2007</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8621</v>
+        <v>1.4442</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.0253</v>
+        <v>-4.1356</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6414</v>
+        <v>-1.5026</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.3839</v>
+        <v>-2.6329</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0812</v>
+        <v>0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8579</v>
+        <v>1.1042</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0092</v>
+        <v>1.4564</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1513</v>
+        <v>-0.3522</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2335</v>
+        <v>1.631</v>
       </c>
       <c r="W4" t="n">
-        <v>0.23</v>
+        <v>2.565</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0035</v>
+        <v>-0.9340000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7411</v>
+        <v>0.4609</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9571</v>
+        <v>3.7696</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.6982</v>
+        <v>-3.3086</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8921</v>
+        <v>1.1749</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7033</v>
+        <v>2.6967</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1887</v>
+        <v>-1.5218</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2435</v>
+        <v>5.2002</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2007</v>
+        <v>4.3381</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4442</v>
+        <v>0.8621</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.1356</v>
+        <v>-4.0253</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5026</v>
+        <v>-1.6414</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.6329</v>
+        <v>-2.3839</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6244</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1044</v>
+        <v>1.1337</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1891</v>
+        <v>1.4612</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2935</v>
+        <v>-0.3275</v>
       </c>
       <c r="V5" t="n">
-        <v>1.631</v>
+        <v>0.2335</v>
       </c>
       <c r="W5" t="n">
-        <v>2.565</v>
+        <v>0.23</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.9340000000000001</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.805</v>
+        <v>-0.0107</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8176</v>
+        <v>2.4063</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6226</v>
+        <v>-2.417</v>
       </c>
       <c r="G6" t="n">
         <v>-2.7777</v>
@@ -922,13 +922,13 @@
         <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4195</v>
+        <v>1.1692</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4469</v>
+        <v>-0.2414</v>
       </c>
       <c r="V6" t="n">
         <v>1.631</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3882</v>
+        <v>-1.9744</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0878</v>
+        <v>0.3254</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4759</v>
+        <v>-2.2998</v>
       </c>
       <c r="G7" t="n">
         <v>-3.9835</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5304</v>
+        <v>0.9442</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0621</v>
+        <v>1.2997</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5317</v>
+        <v>-0.3555</v>
       </c>
       <c r="V7" t="n">
         <v>1.0649</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8669</v>
+        <v>-2.0603</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1014</v>
+        <v>-2.5004</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2345</v>
+        <v>0.4401</v>
       </c>
       <c r="G8" t="n">
         <v>-2.7429</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7483</v>
+        <v>0.0582</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3791</v>
+        <v>0.222</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3692</v>
+        <v>-0.1637</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1278</v>
+        <v>-3.3421</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6574</v>
+        <v>-0.8717</v>
       </c>
       <c r="F9" t="n">
         <v>-2.4704</v>
@@ -1156,10 +1156,10 @@
         <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4939</v>
+        <v>0.2796</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="U9" t="n">
         <v>-0.1024</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6035</v>
+        <v>-4.2043</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9463</v>
+        <v>-2.5177</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6572</v>
+        <v>-1.6866</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8043</v>
@@ -1234,13 +1234,13 @@
         <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1748</v>
+        <v>0.2244</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0529</v>
+        <v>0.3758</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.122</v>
+        <v>-0.1513</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.5288</v>
+        <v>-8.1797</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.4544</v>
+        <v>-6.1934</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0744</v>
+        <v>-1.9863</v>
       </c>
       <c r="G11" t="n">
         <v>-7.5129</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5898</v>
+        <v>0.9388</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9968</v>
+        <v>1.2578</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4071</v>
+        <v>-0.319</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3975</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.6868</v>
+        <v>-11.382</v>
       </c>
       <c r="E12" t="n">
-        <v>8.275299999999998</v>
+        <v>9.580100000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>-20.9621</v>
+        <v>-20.962</v>
       </c>
       <c r="G12" t="n">
         <v>-18.227</v>
@@ -1390,10 +1390,10 @@
         <v>9.3653</v>
       </c>
       <c r="S12" t="n">
-        <v>8.308300000000001</v>
+        <v>9.613199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>10.6825</v>
+        <v>11.9875</v>
       </c>
       <c r="U12" t="n">
         <v>-2.3744</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.055999999999999</v>
+        <v>6.5915</v>
       </c>
       <c r="E13" t="n">
-        <v>8.5884</v>
+        <v>6.5524</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5324</v>
+        <v>0.0391</v>
       </c>
       <c r="G13" t="n">
         <v>3.7419</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4816</v>
+        <v>0.0171</v>
       </c>
       <c r="T13" t="n">
-        <v>3.0623</v>
+        <v>1.0263</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5807</v>
+        <v>-1.0092</v>
       </c>
       <c r="V13" t="n">
         <v>1.1675</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.23</v>
+        <v>4.538</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2672</v>
+        <v>4.4339</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0371</v>
+        <v>0.104</v>
       </c>
       <c r="G14" t="n">
-        <v>3.122</v>
+        <v>2.505</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3839</v>
+        <v>1.0175</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7382</v>
+        <v>1.4875</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5468</v>
+        <v>3.4605</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2044</v>
+        <v>0.8015</v>
       </c>
       <c r="L14" t="n">
-        <v>2.3423</v>
+        <v>2.6591</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4247</v>
+        <v>-0.9555</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1794</v>
+        <v>0.216</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6041</v>
+        <v>-1.1716</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9545</v>
+        <v>-0.8401</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.3896</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4449</v>
+        <v>-1.2297</v>
       </c>
       <c r="V14" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="W14" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.91</v>
+        <v>3.7722</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4695</v>
+        <v>3.6958</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5595</v>
+        <v>0.0764</v>
       </c>
       <c r="G15" t="n">
-        <v>2.505</v>
+        <v>3.122</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0175</v>
+        <v>1.3839</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4875</v>
+        <v>1.7382</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4605</v>
+        <v>3.5468</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8015</v>
+        <v>1.2044</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6591</v>
+        <v>2.3423</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9555</v>
+        <v>-0.4247</v>
       </c>
       <c r="N15" t="n">
-        <v>0.216</v>
+        <v>0.1794</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1716</v>
+        <v>-0.6041</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.468</v>
+        <v>-0.4123</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5748</v>
+        <v>-0.0809</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.8932</v>
+        <v>-0.3314</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4655</v>
+        <v>2.0918</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3866</v>
+        <v>1.8153</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0789</v>
+        <v>0.2765</v>
       </c>
       <c r="G16" t="n">
         <v>0.7418</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2793</v>
+        <v>-0.6531</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6524</v>
+        <v>-0.2238</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6269</v>
+        <v>-0.4292</v>
       </c>
       <c r="V16" t="n">
         <v>2.2112</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GONZALEZ CORDERO</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.027</v>
+        <v>1.8761</v>
       </c>
       <c r="E17" t="n">
-        <v>0.531</v>
+        <v>4.1818</v>
       </c>
       <c r="F17" t="n">
-        <v>0.496</v>
+        <v>-2.3057</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3592</v>
+        <v>3.5047</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0342</v>
+        <v>3.3732</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3249</v>
+        <v>0.1314</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0776</v>
+        <v>4.4928</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0384</v>
+        <v>3.296</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0392</v>
+        <v>1.1969</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2816</v>
+        <v>-0.9881</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0041</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2857</v>
+        <v>-1.0654</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0398</v>
+        <v>-0.2717</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4534</v>
+        <v>0.1458</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4932</v>
+        <v>-0.4175</v>
       </c>
       <c r="V17" t="n">
-        <v>0.7076</v>
+        <v>-1.9813</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7076</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9552</v>
+        <v>1.2373</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5388</v>
+        <v>2.2165</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5836</v>
+        <v>-0.9792</v>
       </c>
       <c r="G18" t="n">
-        <v>3.5047</v>
+        <v>1.2854</v>
       </c>
       <c r="H18" t="n">
-        <v>3.3732</v>
+        <v>1.1474</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1314</v>
+        <v>0.138</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4928</v>
+        <v>1.7062</v>
       </c>
       <c r="K18" t="n">
-        <v>3.296</v>
+        <v>0.9314</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1969</v>
+        <v>0.7748</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9881</v>
+        <v>-0.4208</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.216</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0654</v>
+        <v>-0.6368</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6244</v>
+        <v>1.0406</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1926</v>
+        <v>-0.8587</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4972</v>
+        <v>0.3834</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6954</v>
+        <v>-1.2421</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.9813</v>
+        <v>-0.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5838</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.565</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>A. GONZALEZ CORDERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0332</v>
+        <v>0.8587</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4664</v>
+        <v>0.1023</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4333</v>
+        <v>0.7563</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2854</v>
+        <v>0.3592</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1474</v>
+        <v>0.0342</v>
       </c>
       <c r="I19" t="n">
-        <v>0.138</v>
+        <v>0.3249</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7062</v>
+        <v>0.0776</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9314</v>
+        <v>0.0384</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7748</v>
+        <v>0.0392</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4208</v>
+        <v>0.2816</v>
       </c>
       <c r="N19" t="n">
-        <v>0.216</v>
+        <v>-0.0041</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6368</v>
+        <v>0.2857</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0812</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0628</v>
+        <v>-0.2081</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3667</v>
+        <v>0.0248</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6962</v>
+        <v>-0.2329</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.23</v>
+        <v>0.7076</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3975</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2813</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0396</v>
+        <v>2.1467</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3208</v>
+        <v>-1.4264</v>
       </c>
       <c r="G20" t="n">
         <v>2.9015</v>
@@ -2014,13 +2014,13 @@
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9559</v>
+        <v>-0.9543</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3477</v>
+        <v>0.4548</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.3036</v>
+        <v>-1.4091</v>
       </c>
       <c r="V20" t="n">
         <v>0.23</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8089</v>
+        <v>-2.5237</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2255</v>
+        <v>-1.7784</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5833</v>
+        <v>-0.7453</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0622</v>
+        <v>0.1278</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3941</v>
+        <v>-0.4159</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4564</v>
+        <v>0.5437</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1356</v>
+        <v>-0.4721</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5004</v>
+        <v>-0.5505</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.636</v>
+        <v>0.0784</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0733</v>
+        <v>0.5999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1063</v>
+        <v>0.1346</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1796</v>
+        <v>0.4654</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2487</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3772</v>
+        <v>-0.8378</v>
       </c>
       <c r="T21" t="n">
-        <v>1.6988</v>
+        <v>-0.2657</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3216</v>
+        <v>-0.5721000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8751</v>
+        <v>-1.3975</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9</v>
+        <v>-2.9034</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0999</v>
+        <v>-2.4042</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8001</v>
+        <v>-0.4992</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1278</v>
+        <v>-0.0622</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4159</v>
+        <v>0.3941</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5437</v>
+        <v>-0.4564</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4721</v>
+        <v>-0.1356</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5505</v>
+        <v>0.5004</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0784</v>
+        <v>-0.636</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5999</v>
+        <v>0.0733</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1346</v>
+        <v>-0.1063</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4654</v>
+        <v>0.1796</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4162</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2141</v>
+        <v>0.2827</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.5201</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6269</v>
+        <v>-0.2374</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3975</v>
+        <v>-1.8751</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.3975</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6867</v>
+        <v>16.2588</v>
       </c>
       <c r="E23" t="n">
         <v>20.9621</v>
       </c>
       <c r="F23" t="n">
-        <v>-8.2752</v>
+        <v>-4.7035</v>
       </c>
       <c r="G23" t="n">
         <v>18.2271</v>
@@ -2242,19 +2242,19 @@
         <v>3.1219</v>
       </c>
       <c r="Q23" t="n">
-        <v>-9.365399999999999</v>
+        <v>-9.365399999999998</v>
       </c>
       <c r="R23" t="n">
         <v>12.4871</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.308199999999999</v>
+        <v>-4.7363</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3743</v>
+        <v>2.3744</v>
       </c>
       <c r="U23" t="n">
-        <v>-10.6826</v>
+        <v>-7.1106</v>
       </c>
       <c r="V23" t="n">
         <v>-0.3537999999999999</v>
@@ -2263,7 +2263,7 @@
         <v>6.0499</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.4037</v>
+        <v>-6.403700000000001</v>
       </c>
     </row>
   </sheetData>
